--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125570375</v>
+        <v>125578984</v>
       </c>
       <c r="B2" t="n">
-        <v>80028</v>
+        <v>79932</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522743</v>
+        <v>522652</v>
       </c>
       <c r="R2" t="n">
-        <v>6935007</v>
+        <v>6934983</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125571057</v>
+        <v>125578845</v>
       </c>
       <c r="B3" t="n">
-        <v>98290</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +793,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522672</v>
+        <v>522698</v>
       </c>
       <c r="R3" t="n">
-        <v>6934980</v>
+        <v>6934963</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,17 +863,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Även knärot på växtplatsen</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125570480</v>
+        <v>125570375</v>
       </c>
       <c r="B4" t="n">
         <v>80028</v>
@@ -924,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522727</v>
+        <v>522743</v>
       </c>
       <c r="R4" t="n">
-        <v>6934989</v>
+        <v>6935007</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125570868</v>
+        <v>125571057</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>98290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522696</v>
+        <v>522672</v>
       </c>
       <c r="R5" t="n">
-        <v>6934973</v>
+        <v>6934980</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1062,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Även knärot på växtplatsen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125570749</v>
+        <v>125578922</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,41 +1109,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522706</v>
+        <v>522640</v>
       </c>
       <c r="R6" t="n">
-        <v>6934969</v>
+        <v>6934994</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,17 +1178,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125570288</v>
+        <v>125570480</v>
       </c>
       <c r="B7" t="n">
         <v>80028</v>
@@ -1235,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522749</v>
+        <v>522727</v>
       </c>
       <c r="R7" t="n">
-        <v>6935005</v>
+        <v>6934989</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1297,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125571875</v>
+        <v>125570868</v>
       </c>
       <c r="B8" t="n">
-        <v>91459</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1321,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522618</v>
+        <v>522696</v>
       </c>
       <c r="R8" t="n">
-        <v>6934967</v>
+        <v>6934973</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1399,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125570330</v>
+        <v>125570749</v>
       </c>
       <c r="B9" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,13 +1447,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>522753</v>
+        <v>522706</v>
       </c>
       <c r="R9" t="n">
-        <v>6935009</v>
+        <v>6934969</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,7 +1487,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,7 +1514,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125570109</v>
+        <v>125570288</v>
       </c>
       <c r="B10" t="n">
         <v>80028</v>
@@ -1546,13 +1554,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>522747</v>
+        <v>522749</v>
       </c>
       <c r="R10" t="n">
-        <v>6935015</v>
+        <v>6935005</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125572039</v>
+        <v>125571875</v>
       </c>
       <c r="B11" t="n">
-        <v>80028</v>
+        <v>91459</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1632,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,13 +1656,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522611</v>
+        <v>522618</v>
       </c>
       <c r="R11" t="n">
-        <v>6934976</v>
+        <v>6934967</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1710,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125572644</v>
+        <v>125570330</v>
       </c>
       <c r="B12" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1730,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522706</v>
+        <v>522753</v>
       </c>
       <c r="R12" t="n">
-        <v>6934963</v>
+        <v>6935009</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1790,7 +1798,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125571022</v>
+        <v>125570109</v>
       </c>
       <c r="B13" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1837,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522674</v>
+        <v>522747</v>
       </c>
       <c r="R13" t="n">
-        <v>6934973</v>
+        <v>6935015</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1893,11 +1901,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Även spindelblomster på växtplatsen</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125572346</v>
+        <v>125572644</v>
       </c>
       <c r="B14" t="n">
-        <v>92448</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1939,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522600</v>
+        <v>522706</v>
       </c>
       <c r="R14" t="n">
-        <v>6934975</v>
+        <v>6934963</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2000,6 +2003,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,10 +2034,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125570214</v>
+        <v>125578989</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,41 +2046,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522744</v>
+        <v>522652</v>
       </c>
       <c r="R15" t="n">
-        <v>6935010</v>
+        <v>6934983</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2110,6 +2122,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2128,10 +2141,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125570646</v>
+        <v>125572039</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2157,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,13 +2181,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522721</v>
+        <v>522611</v>
       </c>
       <c r="R16" t="n">
-        <v>6934955</v>
+        <v>6934976</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2227,6 +2240,525 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125571022</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>522674</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6934973</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Även spindelblomster på växtplatsen</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125572346</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>522600</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6934975</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125570214</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>522744</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6935010</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125570646</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>522721</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6934955</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125578935</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80064</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mellan-Vattensjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>522640</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6934994</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125578984</v>
+        <v>125570868</v>
       </c>
       <c r="B2" t="n">
-        <v>79932</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,44 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522652</v>
+        <v>522696</v>
       </c>
       <c r="R2" t="n">
-        <v>6934983</v>
+        <v>6934973</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125578845</v>
+        <v>125578989</v>
       </c>
       <c r="B3" t="n">
         <v>98269</v>
@@ -825,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522698</v>
+        <v>522652</v>
       </c>
       <c r="R3" t="n">
-        <v>6934963</v>
+        <v>6934983</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125570375</v>
+        <v>125570749</v>
       </c>
       <c r="B4" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522743</v>
+        <v>522706</v>
       </c>
       <c r="R4" t="n">
-        <v>6935007</v>
+        <v>6934969</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125571057</v>
+        <v>125571875</v>
       </c>
       <c r="B5" t="n">
-        <v>98290</v>
+        <v>91459</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522672</v>
+        <v>522618</v>
       </c>
       <c r="R5" t="n">
-        <v>6934980</v>
+        <v>6934967</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1066,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Även knärot på växtplatsen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125578922</v>
+        <v>125570109</v>
       </c>
       <c r="B6" t="n">
         <v>80028</v>
@@ -1131,22 +1127,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522640</v>
+        <v>522747</v>
       </c>
       <c r="R6" t="n">
-        <v>6934994</v>
+        <v>6935015</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,7 +1177,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1203,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125570480</v>
+        <v>125578845</v>
       </c>
       <c r="B7" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,41 +1207,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522727</v>
+        <v>522698</v>
       </c>
       <c r="R7" t="n">
-        <v>6934989</v>
+        <v>6934963</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,6 +1283,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1305,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125570868</v>
+        <v>125572346</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
+        <v>92448</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522696</v>
+        <v>522600</v>
       </c>
       <c r="R8" t="n">
-        <v>6934973</v>
+        <v>6934975</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1407,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125570749</v>
+        <v>125572039</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>522706</v>
+        <v>522611</v>
       </c>
       <c r="R9" t="n">
-        <v>6934969</v>
+        <v>6934976</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125570288</v>
+        <v>125570480</v>
       </c>
       <c r="B10" t="n">
         <v>80028</v>
@@ -1554,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>522749</v>
+        <v>522727</v>
       </c>
       <c r="R10" t="n">
-        <v>6935005</v>
+        <v>6934989</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1616,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125571875</v>
+        <v>125570288</v>
       </c>
       <c r="B11" t="n">
-        <v>91459</v>
+        <v>80028</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1632,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,13 +1648,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522618</v>
+        <v>522749</v>
       </c>
       <c r="R11" t="n">
-        <v>6934967</v>
+        <v>6935005</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125570330</v>
+        <v>125578922</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,37 +1726,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522753</v>
+        <v>522640</v>
       </c>
       <c r="R12" t="n">
-        <v>6935009</v>
+        <v>6934994</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,17 +1791,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1825,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125570109</v>
+        <v>125572644</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,25 +1828,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522747</v>
+        <v>522706</v>
       </c>
       <c r="R13" t="n">
-        <v>6935015</v>
+        <v>6934963</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1901,6 +1892,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125572644</v>
+        <v>125570375</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,25 +1935,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,13 +1963,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522706</v>
+        <v>522743</v>
       </c>
       <c r="R14" t="n">
-        <v>6934963</v>
+        <v>6935007</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2003,11 +1999,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2034,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125578989</v>
+        <v>125571057</v>
       </c>
       <c r="B15" t="n">
-        <v>98269</v>
+        <v>98290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,45 +2037,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522652</v>
+        <v>522672</v>
       </c>
       <c r="R15" t="n">
-        <v>6934983</v>
+        <v>6934980</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2116,13 +2103,17 @@
           <t>2025-05-31</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Även knärot på växtplatsen</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2141,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125572039</v>
+        <v>125570646</v>
       </c>
       <c r="B16" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,21 +2148,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2181,13 +2172,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522611</v>
+        <v>522721</v>
       </c>
       <c r="R16" t="n">
-        <v>6934976</v>
+        <v>6934955</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125571022</v>
+        <v>125570214</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2255,25 +2246,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2283,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522674</v>
+        <v>522744</v>
       </c>
       <c r="R17" t="n">
-        <v>6934973</v>
+        <v>6935010</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2319,11 +2310,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Även spindelblomster på växtplatsen</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2350,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125572346</v>
+        <v>125578984</v>
       </c>
       <c r="B18" t="n">
-        <v>92448</v>
+        <v>79932</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2366,37 +2352,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>522600</v>
+        <v>522652</v>
       </c>
       <c r="R18" t="n">
-        <v>6934975</v>
+        <v>6934983</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2434,6 +2423,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2452,10 +2442,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125570214</v>
+        <v>125571022</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2464,25 +2454,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2492,10 +2482,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>522744</v>
+        <v>522674</v>
       </c>
       <c r="R19" t="n">
-        <v>6935010</v>
+        <v>6934973</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2528,6 +2518,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Även spindelblomster på växtplatsen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2554,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125570646</v>
+        <v>125578935</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
+        <v>80064</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2566,38 +2561,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>522721</v>
+        <v>522640</v>
       </c>
       <c r="R20" t="n">
-        <v>6934955</v>
+        <v>6934994</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,6 +2636,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2656,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125578935</v>
+        <v>125570330</v>
       </c>
       <c r="B21" t="n">
-        <v>80064</v>
+        <v>57632</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2668,44 +2667,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522640</v>
+        <v>522753</v>
       </c>
       <c r="R21" t="n">
-        <v>6934994</v>
+        <v>6935009</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2737,13 +2733,17 @@
           <t>2025-05-31</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125570868</v>
+        <v>125570375</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522696</v>
+        <v>522743</v>
       </c>
       <c r="R2" t="n">
-        <v>6934973</v>
+        <v>6935007</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,57 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125578989</v>
+        <v>125570288</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522652</v>
+        <v>522749</v>
       </c>
       <c r="R3" t="n">
-        <v>6934983</v>
+        <v>6935005</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125570749</v>
+        <v>125571022</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522706</v>
+        <v>522674</v>
       </c>
       <c r="R4" t="n">
-        <v>6934969</v>
+        <v>6934973</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Även spindelblomster på växtplatsen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125571875</v>
+        <v>125570480</v>
       </c>
       <c r="B5" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522618</v>
+        <v>522727</v>
       </c>
       <c r="R5" t="n">
-        <v>6934967</v>
+        <v>6934989</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,37 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125570109</v>
+        <v>125572346</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522747</v>
+        <v>522600</v>
       </c>
       <c r="R6" t="n">
-        <v>6935015</v>
+        <v>6934975</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,57 +1165,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125578845</v>
+        <v>125570868</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522698</v>
+        <v>522696</v>
       </c>
       <c r="R7" t="n">
-        <v>6934963</v>
+        <v>6934973</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,7 +1244,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,37 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125572346</v>
+        <v>125570330</v>
       </c>
       <c r="B8" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522600</v>
+        <v>522753</v>
       </c>
       <c r="R8" t="n">
-        <v>6934975</v>
+        <v>6935009</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1378,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,15 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125572039</v>
+        <v>125570109</v>
       </c>
       <c r="B9" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,13 +1399,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>522611</v>
+        <v>522747</v>
       </c>
       <c r="R9" t="n">
-        <v>6934976</v>
+        <v>6935015</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1506,37 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125570480</v>
+        <v>125572644</v>
       </c>
       <c r="B10" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>522727</v>
+        <v>522706</v>
       </c>
       <c r="R10" t="n">
-        <v>6934989</v>
+        <v>6934963</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,15 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125570288</v>
+        <v>125572039</v>
       </c>
       <c r="B11" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522749</v>
+        <v>522611</v>
       </c>
       <c r="R11" t="n">
-        <v>6935005</v>
+        <v>6934976</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1710,37 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125578922</v>
+        <v>125578984</v>
       </c>
       <c r="B12" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522640</v>
+        <v>522652</v>
       </c>
       <c r="R12" t="n">
-        <v>6934994</v>
+        <v>6934983</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,15 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125572644</v>
+        <v>125578845</v>
       </c>
       <c r="B13" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,19 +1790,23 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522706</v>
+        <v>522698</v>
       </c>
       <c r="R13" t="n">
         <v>6934963</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1894,17 +1838,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1923,37 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125570375</v>
+        <v>125570749</v>
       </c>
       <c r="B14" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522743</v>
+        <v>522706</v>
       </c>
       <c r="R14" t="n">
-        <v>6935007</v>
+        <v>6934969</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1999,6 +1934,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,53 +1965,51 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125571057</v>
+        <v>125578922</v>
       </c>
       <c r="B15" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522672</v>
+        <v>522640</v>
       </c>
       <c r="R15" t="n">
-        <v>6934980</v>
+        <v>6934994</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,17 +2041,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Även knärot på växtplatsen</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2132,15 +2066,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125570646</v>
+        <v>125571875</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,21 +2077,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,13 +2101,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522721</v>
+        <v>522618</v>
       </c>
       <c r="R16" t="n">
-        <v>6934955</v>
+        <v>6934967</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2234,53 +2163,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125570214</v>
+        <v>125578989</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522744</v>
+        <v>522652</v>
       </c>
       <c r="R17" t="n">
-        <v>6935010</v>
+        <v>6934983</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2318,6 +2246,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2336,15 +2265,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125578984</v>
+        <v>125571057</v>
       </c>
       <c r="B18" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,40 +2276,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>522652</v>
+        <v>522672</v>
       </c>
       <c r="R18" t="n">
-        <v>6934983</v>
+        <v>6934980</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2417,13 +2338,17 @@
           <t>2025-05-31</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Även knärot på växtplatsen</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2442,53 +2367,51 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125571022</v>
+        <v>125578935</v>
       </c>
       <c r="B19" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>522674</v>
+        <v>522640</v>
       </c>
       <c r="R19" t="n">
-        <v>6934973</v>
+        <v>6934994</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2520,17 +2443,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Även spindelblomster på växtplatsen</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2549,56 +2468,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125578935</v>
+        <v>125570214</v>
       </c>
       <c r="B20" t="n">
-        <v>80064</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>522640</v>
+        <v>522744</v>
       </c>
       <c r="R20" t="n">
-        <v>6934994</v>
+        <v>6935010</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2636,7 +2547,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2655,15 +2565,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125570330</v>
+        <v>125570646</v>
       </c>
       <c r="B21" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,21 +2576,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2695,13 +2600,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522753</v>
+        <v>522721</v>
       </c>
       <c r="R21" t="n">
-        <v>6935009</v>
+        <v>6934955</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2731,11 +2636,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -2066,48 +2066,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125571875</v>
+        <v>125578989</v>
       </c>
       <c r="B16" t="n">
-        <v>91513</v>
+        <v>98324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522618</v>
+        <v>522652</v>
       </c>
       <c r="R16" t="n">
-        <v>6934967</v>
+        <v>6934983</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2145,6 +2149,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,52 +2168,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125578989</v>
+        <v>125571875</v>
       </c>
       <c r="B17" t="n">
-        <v>98324</v>
+        <v>91513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522652</v>
+        <v>522618</v>
       </c>
       <c r="R17" t="n">
-        <v>6934983</v>
+        <v>6934967</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2246,7 +2247,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125571022</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125572346</v>
       </c>
       <c r="B6" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>125572644</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,37 +1660,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125578984</v>
+        <v>125578845</v>
       </c>
       <c r="B12" t="n">
-        <v>79974</v>
+        <v>98331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1698,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522652</v>
+        <v>522698</v>
       </c>
       <c r="R12" t="n">
-        <v>6934983</v>
+        <v>6934963</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1761,38 +1762,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125578845</v>
+        <v>125578984</v>
       </c>
       <c r="B13" t="n">
-        <v>98324</v>
+        <v>79974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522698</v>
+        <v>522652</v>
       </c>
       <c r="R13" t="n">
-        <v>6934963</v>
+        <v>6934983</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,7 +1866,7 @@
         <v>125570749</v>
       </c>
       <c r="B14" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,52 +2066,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125578989</v>
+        <v>125571875</v>
       </c>
       <c r="B16" t="n">
-        <v>98324</v>
+        <v>91520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522652</v>
+        <v>522618</v>
       </c>
       <c r="R16" t="n">
-        <v>6934983</v>
+        <v>6934967</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2149,7 +2145,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2168,32 +2163,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125571875</v>
+        <v>125571057</v>
       </c>
       <c r="B17" t="n">
-        <v>91513</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522618</v>
+        <v>522672</v>
       </c>
       <c r="R17" t="n">
-        <v>6934967</v>
+        <v>6934980</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2239,6 +2234,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Även knärot på växtplatsen</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2265,48 +2265,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125571057</v>
+        <v>125578989</v>
       </c>
       <c r="B18" t="n">
-        <v>98345</v>
+        <v>98331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>522672</v>
+        <v>522652</v>
       </c>
       <c r="R18" t="n">
-        <v>6934980</v>
+        <v>6934983</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2338,17 +2342,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Även knärot på växtplatsen</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -2066,32 +2066,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125571875</v>
+        <v>125571057</v>
       </c>
       <c r="B16" t="n">
-        <v>91520</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522618</v>
+        <v>522672</v>
       </c>
       <c r="R16" t="n">
-        <v>6934967</v>
+        <v>6934980</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2137,6 +2137,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Även knärot på växtplatsen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2163,48 +2168,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125571057</v>
+        <v>125578989</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>98331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522672</v>
+        <v>522652</v>
       </c>
       <c r="R17" t="n">
-        <v>6934980</v>
+        <v>6934983</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2236,17 +2245,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Även knärot på växtplatsen</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2265,52 +2270,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125578989</v>
+        <v>125571875</v>
       </c>
       <c r="B18" t="n">
-        <v>98331</v>
+        <v>91520</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>522652</v>
+        <v>522618</v>
       </c>
       <c r="R18" t="n">
-        <v>6934983</v>
+        <v>6934967</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2348,7 +2349,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125570375</v>
       </c>
       <c r="B2" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125570288</v>
+        <v>125571022</v>
       </c>
       <c r="B3" t="n">
-        <v>80070</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522749</v>
+        <v>522674</v>
       </c>
       <c r="R3" t="n">
-        <v>6935005</v>
+        <v>6934973</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Även spindelblomster på växtplatsen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125571022</v>
+        <v>125570288</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +909,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522674</v>
+        <v>522749</v>
       </c>
       <c r="R4" t="n">
-        <v>6934973</v>
+        <v>6935005</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även spindelblomster på växtplatsen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125570480</v>
+        <v>125572346</v>
       </c>
       <c r="B5" t="n">
-        <v>80070</v>
+        <v>92518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522727</v>
+        <v>522600</v>
       </c>
       <c r="R5" t="n">
-        <v>6934989</v>
+        <v>6934975</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125572346</v>
+        <v>125570480</v>
       </c>
       <c r="B6" t="n">
-        <v>92509</v>
+        <v>80071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522600</v>
+        <v>522727</v>
       </c>
       <c r="R6" t="n">
-        <v>6934975</v>
+        <v>6934989</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125570868</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>125570109</v>
       </c>
       <c r="B9" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>125572644</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125572039</v>
       </c>
       <c r="B11" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,38 +1660,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125578845</v>
+        <v>125578984</v>
       </c>
       <c r="B12" t="n">
-        <v>98331</v>
+        <v>79975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1699,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522698</v>
+        <v>522652</v>
       </c>
       <c r="R12" t="n">
-        <v>6934963</v>
+        <v>6934983</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,37 +1761,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125578984</v>
+        <v>125578845</v>
       </c>
       <c r="B13" t="n">
-        <v>79974</v>
+        <v>98334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522652</v>
+        <v>522698</v>
       </c>
       <c r="R13" t="n">
-        <v>6934983</v>
+        <v>6934963</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,7 +1866,7 @@
         <v>125570749</v>
       </c>
       <c r="B14" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>125578922</v>
       </c>
       <c r="B15" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,32 +2066,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125571057</v>
+        <v>125571875</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>91524</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522672</v>
+        <v>522618</v>
       </c>
       <c r="R16" t="n">
-        <v>6934980</v>
+        <v>6934967</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2137,11 +2137,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Även knärot på växtplatsen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2168,52 +2163,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125578989</v>
+        <v>125571057</v>
       </c>
       <c r="B17" t="n">
-        <v>98331</v>
+        <v>98355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522652</v>
+        <v>522672</v>
       </c>
       <c r="R17" t="n">
-        <v>6934983</v>
+        <v>6934980</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2245,13 +2236,17 @@
           <t>2025-05-31</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Även knärot på växtplatsen</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2270,48 +2265,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125571875</v>
+        <v>125578989</v>
       </c>
       <c r="B18" t="n">
-        <v>91520</v>
+        <v>98334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>522618</v>
+        <v>522652</v>
       </c>
       <c r="R18" t="n">
-        <v>6934967</v>
+        <v>6934983</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2349,6 +2348,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>125578935</v>
       </c>
       <c r="B19" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>125570214</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>125570646</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125570375</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125571022</v>
+        <v>125570288</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522674</v>
+        <v>522749</v>
       </c>
       <c r="R3" t="n">
-        <v>6934973</v>
+        <v>6935005</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Även spindelblomster på växtplatsen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125570288</v>
+        <v>125571022</v>
       </c>
       <c r="B4" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522749</v>
+        <v>522674</v>
       </c>
       <c r="R4" t="n">
-        <v>6935005</v>
+        <v>6934973</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även spindelblomster på växtplatsen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,7 +974,7 @@
         <v>125572346</v>
       </c>
       <c r="B5" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125570480</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125570868</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>125570109</v>
       </c>
       <c r="B9" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>125572644</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125572039</v>
       </c>
       <c r="B11" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,37 +1660,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125578984</v>
+        <v>125578845</v>
       </c>
       <c r="B12" t="n">
-        <v>79975</v>
+        <v>98338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1698,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522652</v>
+        <v>522698</v>
       </c>
       <c r="R12" t="n">
-        <v>6934983</v>
+        <v>6934963</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1761,38 +1762,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125578845</v>
+        <v>125578984</v>
       </c>
       <c r="B13" t="n">
-        <v>98334</v>
+        <v>79979</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522698</v>
+        <v>522652</v>
       </c>
       <c r="R13" t="n">
-        <v>6934963</v>
+        <v>6934983</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,48 +1863,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125570749</v>
+        <v>125578922</v>
       </c>
       <c r="B14" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522706</v>
+        <v>522640</v>
       </c>
       <c r="R14" t="n">
-        <v>6934969</v>
+        <v>6934994</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1936,17 +1939,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1965,51 +1964,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125578922</v>
+        <v>125570749</v>
       </c>
       <c r="B15" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522640</v>
+        <v>522706</v>
       </c>
       <c r="R15" t="n">
-        <v>6934994</v>
+        <v>6934969</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2041,13 +2037,17 @@
           <t>2025-05-31</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,32 +2066,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125571875</v>
+        <v>125571057</v>
       </c>
       <c r="B16" t="n">
-        <v>91524</v>
+        <v>98359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522618</v>
+        <v>522672</v>
       </c>
       <c r="R16" t="n">
-        <v>6934967</v>
+        <v>6934980</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2137,6 +2137,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Även knärot på växtplatsen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2163,48 +2168,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125571057</v>
+        <v>125578989</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522672</v>
+        <v>522652</v>
       </c>
       <c r="R17" t="n">
-        <v>6934980</v>
+        <v>6934983</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2236,17 +2245,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Även knärot på växtplatsen</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2265,52 +2270,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125578989</v>
+        <v>125571875</v>
       </c>
       <c r="B18" t="n">
-        <v>98334</v>
+        <v>91528</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>522652</v>
+        <v>522618</v>
       </c>
       <c r="R18" t="n">
-        <v>6934983</v>
+        <v>6934967</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2348,7 +2349,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>125578935</v>
       </c>
       <c r="B19" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>125570214</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>125570646</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -2066,48 +2066,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125571057</v>
+        <v>125578989</v>
       </c>
       <c r="B16" t="n">
-        <v>98359</v>
+        <v>98338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522672</v>
+        <v>522652</v>
       </c>
       <c r="R16" t="n">
-        <v>6934980</v>
+        <v>6934983</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2139,17 +2143,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Även knärot på växtplatsen</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2168,52 +2168,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125578989</v>
+        <v>125571057</v>
       </c>
       <c r="B17" t="n">
-        <v>98338</v>
+        <v>98359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522652</v>
+        <v>522672</v>
       </c>
       <c r="R17" t="n">
-        <v>6934983</v>
+        <v>6934980</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2245,13 +2241,17 @@
           <t>2025-05-31</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Även knärot på växtplatsen</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125571022</v>
       </c>
       <c r="B4" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125572346</v>
+        <v>125570480</v>
       </c>
       <c r="B5" t="n">
-        <v>92522</v>
+        <v>80075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522600</v>
+        <v>522727</v>
       </c>
       <c r="R5" t="n">
-        <v>6934975</v>
+        <v>6934989</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125570480</v>
+        <v>125572346</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>92522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522727</v>
+        <v>522600</v>
       </c>
       <c r="R6" t="n">
-        <v>6934989</v>
+        <v>6934975</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>125572644</v>
       </c>
       <c r="B10" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>125578845</v>
       </c>
       <c r="B12" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,51 +1863,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125578922</v>
+        <v>125570749</v>
       </c>
       <c r="B14" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522640</v>
+        <v>522706</v>
       </c>
       <c r="R14" t="n">
-        <v>6934994</v>
+        <v>6934969</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1939,13 +1936,17 @@
           <t>2025-05-31</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1964,48 +1965,51 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125570749</v>
+        <v>125578922</v>
       </c>
       <c r="B15" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522706</v>
+        <v>522640</v>
       </c>
       <c r="R15" t="n">
-        <v>6934969</v>
+        <v>6934994</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2037,17 +2041,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,52 +2066,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125578989</v>
+        <v>125571875</v>
       </c>
       <c r="B16" t="n">
-        <v>98338</v>
+        <v>91528</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522652</v>
+        <v>522618</v>
       </c>
       <c r="R16" t="n">
-        <v>6934983</v>
+        <v>6934967</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2149,7 +2145,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2168,48 +2163,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125571057</v>
+        <v>125578989</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>98339</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522672</v>
+        <v>522652</v>
       </c>
       <c r="R17" t="n">
-        <v>6934980</v>
+        <v>6934983</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2241,17 +2240,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Även knärot på växtplatsen</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2270,32 +2265,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125571875</v>
+        <v>125571057</v>
       </c>
       <c r="B18" t="n">
-        <v>91528</v>
+        <v>98360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2305,10 +2300,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>522618</v>
+        <v>522672</v>
       </c>
       <c r="R18" t="n">
-        <v>6934967</v>
+        <v>6934980</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2341,6 +2336,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Även knärot på växtplatsen</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125570288</v>
+        <v>125571022</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522749</v>
+        <v>522674</v>
       </c>
       <c r="R3" t="n">
-        <v>6935005</v>
+        <v>6934973</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Även spindelblomster på växtplatsen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125571022</v>
+        <v>125570288</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +909,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522674</v>
+        <v>522749</v>
       </c>
       <c r="R4" t="n">
-        <v>6934973</v>
+        <v>6935005</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även spindelblomster på växtplatsen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1660,38 +1660,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125578845</v>
+        <v>125578984</v>
       </c>
       <c r="B12" t="n">
-        <v>98339</v>
+        <v>79979</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1699,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522698</v>
+        <v>522652</v>
       </c>
       <c r="R12" t="n">
-        <v>6934963</v>
+        <v>6934983</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,37 +1761,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125578984</v>
+        <v>125578845</v>
       </c>
       <c r="B13" t="n">
-        <v>79979</v>
+        <v>98339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522652</v>
+        <v>522698</v>
       </c>
       <c r="R13" t="n">
-        <v>6934983</v>
+        <v>6934963</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -2066,48 +2066,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125571875</v>
+        <v>125578989</v>
       </c>
       <c r="B16" t="n">
-        <v>91528</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522618</v>
+        <v>522652</v>
       </c>
       <c r="R16" t="n">
-        <v>6934967</v>
+        <v>6934983</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2145,6 +2149,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,52 +2168,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125578989</v>
+        <v>125571057</v>
       </c>
       <c r="B17" t="n">
-        <v>98339</v>
+        <v>98360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522652</v>
+        <v>522672</v>
       </c>
       <c r="R17" t="n">
-        <v>6934983</v>
+        <v>6934980</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2240,13 +2241,17 @@
           <t>2025-05-31</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Även knärot på växtplatsen</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2265,32 +2270,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125571057</v>
+        <v>125571875</v>
       </c>
       <c r="B18" t="n">
-        <v>98360</v>
+        <v>91528</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2300,10 +2305,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>522672</v>
+        <v>522618</v>
       </c>
       <c r="R18" t="n">
-        <v>6934980</v>
+        <v>6934967</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2336,11 +2341,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Även knärot på växtplatsen</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125570375</v>
       </c>
       <c r="B2" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125571022</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125570288</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125570480</v>
+        <v>125572346</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>92524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522727</v>
+        <v>522600</v>
       </c>
       <c r="R5" t="n">
-        <v>6934989</v>
+        <v>6934975</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125572346</v>
+        <v>125570480</v>
       </c>
       <c r="B6" t="n">
-        <v>92522</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522600</v>
+        <v>522727</v>
       </c>
       <c r="R6" t="n">
-        <v>6934975</v>
+        <v>6934989</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125570868</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125570330</v>
       </c>
       <c r="B8" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>125570109</v>
       </c>
       <c r="B9" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>125572644</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125572039</v>
       </c>
       <c r="B11" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>125578984</v>
       </c>
       <c r="B12" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>125578845</v>
       </c>
       <c r="B13" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,48 +1863,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125570749</v>
+        <v>125578922</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522706</v>
+        <v>522640</v>
       </c>
       <c r="R14" t="n">
-        <v>6934969</v>
+        <v>6934994</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1936,17 +1939,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1965,51 +1964,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125578922</v>
+        <v>125570749</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522640</v>
+        <v>522706</v>
       </c>
       <c r="R15" t="n">
-        <v>6934994</v>
+        <v>6934969</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2041,13 +2037,17 @@
           <t>2025-05-31</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,52 +2066,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125578989</v>
+        <v>125571875</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>91530</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522652</v>
+        <v>522618</v>
       </c>
       <c r="R16" t="n">
-        <v>6934983</v>
+        <v>6934967</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2149,7 +2145,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2171,7 +2166,7 @@
         <v>125571057</v>
       </c>
       <c r="B17" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2270,48 +2265,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125571875</v>
+        <v>125578989</v>
       </c>
       <c r="B18" t="n">
-        <v>91528</v>
+        <v>98341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>522618</v>
+        <v>522652</v>
       </c>
       <c r="R18" t="n">
-        <v>6934967</v>
+        <v>6934983</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2349,6 +2348,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>125578935</v>
       </c>
       <c r="B19" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>125570214</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>125570646</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -1660,37 +1660,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125578984</v>
+        <v>125578845</v>
       </c>
       <c r="B12" t="n">
-        <v>79980</v>
+        <v>98341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1698,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522652</v>
+        <v>522698</v>
       </c>
       <c r="R12" t="n">
-        <v>6934983</v>
+        <v>6934963</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1761,38 +1762,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125578845</v>
+        <v>125578984</v>
       </c>
       <c r="B13" t="n">
-        <v>98341</v>
+        <v>79980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522698</v>
+        <v>522652</v>
       </c>
       <c r="R13" t="n">
-        <v>6934963</v>
+        <v>6934983</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,51 +1863,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125578922</v>
+        <v>125570749</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>98341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522640</v>
+        <v>522706</v>
       </c>
       <c r="R14" t="n">
-        <v>6934994</v>
+        <v>6934969</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1939,13 +1936,17 @@
           <t>2025-05-31</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1964,48 +1965,51 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125570749</v>
+        <v>125578922</v>
       </c>
       <c r="B15" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522706</v>
+        <v>522640</v>
       </c>
       <c r="R15" t="n">
-        <v>6934969</v>
+        <v>6934994</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2037,17 +2041,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125571022</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125572346</v>
+        <v>125570480</v>
       </c>
       <c r="B5" t="n">
-        <v>92524</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522600</v>
+        <v>522727</v>
       </c>
       <c r="R5" t="n">
-        <v>6934975</v>
+        <v>6934989</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125570480</v>
+        <v>125572346</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>92526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522727</v>
+        <v>522600</v>
       </c>
       <c r="R6" t="n">
-        <v>6934989</v>
+        <v>6934975</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>125572644</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,38 +1660,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125578845</v>
+        <v>125578984</v>
       </c>
       <c r="B12" t="n">
-        <v>98341</v>
+        <v>79980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1699,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522698</v>
+        <v>522652</v>
       </c>
       <c r="R12" t="n">
-        <v>6934963</v>
+        <v>6934983</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,37 +1761,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125578984</v>
+        <v>125578845</v>
       </c>
       <c r="B13" t="n">
-        <v>79980</v>
+        <v>98343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522652</v>
+        <v>522698</v>
       </c>
       <c r="R13" t="n">
-        <v>6934983</v>
+        <v>6934963</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,48 +1863,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125570749</v>
+        <v>125578922</v>
       </c>
       <c r="B14" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522706</v>
+        <v>522640</v>
       </c>
       <c r="R14" t="n">
-        <v>6934969</v>
+        <v>6934994</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1936,17 +1939,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1965,51 +1964,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125578922</v>
+        <v>125570749</v>
       </c>
       <c r="B15" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mellan-Vattensjön, Mpd</t>
+          <t>Mellan-Vattensjön, Mellan-Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522640</v>
+        <v>522706</v>
       </c>
       <c r="R15" t="n">
-        <v>6934994</v>
+        <v>6934969</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2041,13 +2037,17 @@
           <t>2025-05-31</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>125571875</v>
       </c>
       <c r="B16" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>125571057</v>
       </c>
       <c r="B17" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>125578989</v>
       </c>
       <c r="B18" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -1660,37 +1660,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125578984</v>
+        <v>125578845</v>
       </c>
       <c r="B12" t="n">
-        <v>79980</v>
+        <v>98343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1698,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522652</v>
+        <v>522698</v>
       </c>
       <c r="R12" t="n">
-        <v>6934983</v>
+        <v>6934963</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1761,38 +1762,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125578845</v>
+        <v>125578984</v>
       </c>
       <c r="B13" t="n">
-        <v>98343</v>
+        <v>79980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522698</v>
+        <v>522652</v>
       </c>
       <c r="R13" t="n">
-        <v>6934963</v>
+        <v>6934983</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125571022</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125572346</v>
       </c>
       <c r="B6" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>125572644</v>
       </c>
       <c r="B10" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,38 +1660,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125578845</v>
+        <v>125578984</v>
       </c>
       <c r="B12" t="n">
-        <v>98343</v>
+        <v>79980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1699,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522698</v>
+        <v>522652</v>
       </c>
       <c r="R12" t="n">
-        <v>6934963</v>
+        <v>6934983</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,37 +1761,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125578984</v>
+        <v>125578845</v>
       </c>
       <c r="B13" t="n">
-        <v>79980</v>
+        <v>98345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522652</v>
+        <v>522698</v>
       </c>
       <c r="R13" t="n">
-        <v>6934983</v>
+        <v>6934963</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
         <v>125570749</v>
       </c>
       <c r="B15" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>125571875</v>
       </c>
       <c r="B16" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>125571057</v>
       </c>
       <c r="B17" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>125578989</v>
       </c>
       <c r="B18" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -1265,7 +1265,7 @@
         <v>125570330</v>
       </c>
       <c r="B8" t="n">
-        <v>57649</v>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -1265,7 +1265,7 @@
         <v>125570330</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -1265,7 +1265,7 @@
         <v>125570330</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -1265,7 +1265,7 @@
         <v>125570330</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -1265,7 +1265,7 @@
         <v>125570330</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -1265,7 +1265,7 @@
         <v>125570330</v>
       </c>
       <c r="B8" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26473-2025 artfynd.xlsx
+++ b/artfynd/A 26473-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441975</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571875</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503642</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125572346</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570214</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570646</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570868</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1465,6 +1505,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503672</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1562,6 +1607,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503673</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1663,6 +1713,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125578984</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1760,6 +1815,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122277262</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1857,6 +1917,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570109</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1954,6 +2019,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570165</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2051,6 +2121,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570288</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2148,6 +2223,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570375</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2245,6 +2325,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570480</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2342,6 +2427,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125572039</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,6 +2533,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125578922</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503645</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570119</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2738,6 +2843,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125578935</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2840,6 +2950,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570330</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2948,6 +3063,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503682</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3050,6 +3170,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570749</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3152,6 +3277,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571022</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3254,6 +3384,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125572644</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3356,6 +3491,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125578845</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3458,6 +3598,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125578989</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3560,8 +3705,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571057</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>